--- a/data/H2DS_practicalData.xlsx
+++ b/data/H2DS_practicalData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scottishmarineinstitute-my.sharepoint.com/personal/sa04ts_sams_ac_uk/Documents/Teaching/H2DS_Practicals/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_F25DC773A252ABDACC1048DE795D750A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2370C1E4-EDE2-4E35-9684-644FC505EE74}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_F25DC773A252ABDACC1048DE795D750A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F60BEABF-B20E-451D-B54E-5EEFF13CE53E}"/>
   <bookViews>
-    <workbookView xWindow="3795" yWindow="1050" windowWidth="20745" windowHeight="13125" tabRatio="778" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23828" yWindow="489" windowWidth="19562" windowHeight="13096" tabRatio="778" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PhosphateCalibration" sheetId="10" r:id="rId1"/>
@@ -18,12 +18,13 @@
     <sheet name="Scallop %fat" sheetId="2" r:id="rId3"/>
     <sheet name="Settling velocity" sheetId="3" r:id="rId4"/>
     <sheet name="Cod lengths" sheetId="13" r:id="rId5"/>
-    <sheet name="Hake" sheetId="4" r:id="rId6"/>
-    <sheet name="Mood shrimp" sheetId="6" r:id="rId7"/>
-    <sheet name="Radon (ppb)" sheetId="7" r:id="rId8"/>
-    <sheet name="LimpetDist" sheetId="8" r:id="rId9"/>
-    <sheet name="Beetles" sheetId="11" r:id="rId10"/>
-    <sheet name="Leaching" sheetId="12" r:id="rId11"/>
+    <sheet name="SmoltWeights" sheetId="14" r:id="rId6"/>
+    <sheet name="Hake" sheetId="4" r:id="rId7"/>
+    <sheet name="Mood shrimp" sheetId="6" r:id="rId8"/>
+    <sheet name="Radon (ppb)" sheetId="7" r:id="rId9"/>
+    <sheet name="LimpetDist" sheetId="8" r:id="rId10"/>
+    <sheet name="Beetles" sheetId="11" r:id="rId11"/>
+    <sheet name="Leaching" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="36">
   <si>
     <t>Scallop % fat</t>
   </si>
@@ -148,6 +149,12 @@
   </si>
   <si>
     <t>CodLength_cm</t>
+  </si>
+  <si>
+    <t>fish_id</t>
+  </si>
+  <si>
+    <t>weight_g</t>
   </si>
 </sst>
 </file>
@@ -496,11 +503,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3D1538-B610-444F-98E6-58BE8E61A8DD}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -565,92 +572,112 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E034C9-4372-4851-9EBB-9B4B3E7019D9}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB45085-AC66-4EBB-96CD-CBCDDA6B08B6}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.125" style="2"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>8.98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3">
-        <v>8.14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>29.5</v>
-      </c>
-      <c r="B4" s="3">
-        <v>6.67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>43</v>
-      </c>
-      <c r="B5" s="3">
-        <v>6.08</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>53</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>62.5</v>
-      </c>
-      <c r="B7" s="3">
-        <v>5.83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>75.5</v>
-      </c>
-      <c r="B8" s="3">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>85</v>
-      </c>
-      <c r="B9" s="3">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>97</v>
+      </c>
+      <c r="B2" s="2">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>83</v>
+      </c>
+      <c r="B3" s="2">
+        <v>98</v>
+      </c>
+      <c r="C3" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>90</v>
+      </c>
+      <c r="B4" s="2">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>93</v>
       </c>
-      <c r="B10" s="3">
-        <v>3.72</v>
+      <c r="B5" s="2">
+        <v>70</v>
+      </c>
+      <c r="C5" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>71</v>
+      </c>
+      <c r="B6" s="2">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>102</v>
+      </c>
+      <c r="B7" s="2">
+        <v>64</v>
+      </c>
+      <c r="C7" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>88</v>
+      </c>
+      <c r="B8" s="2">
+        <v>75</v>
+      </c>
+      <c r="C8" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>94</v>
+      </c>
+      <c r="B9" s="2">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -660,11 +687,106 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E034C9-4372-4851-9EBB-9B4B3E7019D9}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>43</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>53</v>
+      </c>
+      <c r="B6" s="3">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>75.5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>93</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF907D9E-82FA-4445-AC9C-BA609D5EA290}">
   <dimension ref="A1:F148"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -3635,13 +3757,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7B3ECD-B83E-4A68-A3AC-02C2A2121A8E}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="7"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.125" style="7"/>
+    <col min="2" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -3652,7 +3774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>13.075994593666813</v>
       </c>
@@ -3663,7 +3785,7 @@
         <v>14.200000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>11.539232104431052</v>
       </c>
@@ -3674,7 +3796,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>12.349946422902706</v>
       </c>
@@ -3685,7 +3807,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>12.817138357132189</v>
       </c>
@@ -3696,7 +3818,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>10.771565473493888</v>
       </c>
@@ -3716,10 +3838,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87754AC2-9BAB-4D2B-83C7-C2F7231C000C}">
   <dimension ref="A1:A50"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -3981,10 +4103,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3457211-793E-49F3-BDCC-F011151B0A0A}">
   <dimension ref="A1:A201"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -5001,9 +5123,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C65C1-EBBC-49A4-AAF9-F2102F88C85C}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -5118,12 +5240,300 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C3DD7B-AA13-4721-90CD-062924BCB675}">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>48.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B6EA9B-E5A4-4CE8-A9E3-7C5C03522817}">
   <dimension ref="A1:B500"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.125" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -9124,164 +9534,6 @@
       </c>
       <c r="B500" s="2">
         <v>958</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2D27F1-20DC-40D2-A970-DD52A0A641A4}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9291,12 +9543,170 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2D27F1-20DC-40D2-A970-DD52A0A641A4}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9.125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA85986D-F53B-4C81-9092-7C419560398F}">
   <dimension ref="A1:A251"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.9" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="16.125" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -10557,119 +10967,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB45085-AC66-4EBB-96CD-CBCDDA6B08B6}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="12.7109375" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>97</v>
-      </c>
-      <c r="B2" s="2">
-        <v>66</v>
-      </c>
-      <c r="C2" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>83</v>
-      </c>
-      <c r="B3" s="2">
-        <v>98</v>
-      </c>
-      <c r="C3" s="2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>90</v>
-      </c>
-      <c r="B4" s="2">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>93</v>
-      </c>
-      <c r="B5" s="2">
-        <v>70</v>
-      </c>
-      <c r="C5" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>71</v>
-      </c>
-      <c r="B6" s="2">
-        <v>89</v>
-      </c>
-      <c r="C6" s="2">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>102</v>
-      </c>
-      <c r="B7" s="2">
-        <v>64</v>
-      </c>
-      <c r="C7" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>88</v>
-      </c>
-      <c r="B8" s="2">
-        <v>75</v>
-      </c>
-      <c r="C8" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>94</v>
-      </c>
-      <c r="B9" s="2">
-        <v>61</v>
-      </c>
-      <c r="C9" s="2">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>